--- a/sku-servidor/public/layout-productos.xlsx
+++ b/sku-servidor/public/layout-productos.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUGERIDO" sheetId="1" r:id="R527a68f403384dd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EJEMPLOS" sheetId="2" r:id="R07a61bfedd854ce7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUGERIDO" sheetId="1" r:id="R59235e9c1a5e482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EJEMPLOS" sheetId="2" r:id="R5e8b5700522c4e4d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5795,7 +5795,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="7" t="str">
-        <x:v>H: descripción. I: precio público institucional. J: ruta. K: despacho. Precios con IVA.</x:v>
+        <x:v>H: descripción. I: precio público institucional. J: ruta. K: despacho. Precios con el impuesto del maestro incluido.</x:v>
       </x:c>
       <x:c r="B10" s="7"/>
       <x:c r="C10" s="7"/>
@@ -5822,7 +5822,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="7" t="str">
-        <x:v>N: selecciona 0%, 8% o 16%. O: unidad de medida. S: ACTIVO o INACTIVO.</x:v>
+        <x:v>N: 0% sin IVA, 8% IEPS o 16% IVA. O: unidad de medida. S: ACTIVO o INACTIVO.</x:v>
       </x:c>
       <x:c r="B11" s="7"/>
       <x:c r="C11" s="7"/>
